--- a/docs/collections/agrifarm/metadata/data.xlsx
+++ b/docs/collections/agrifarm/metadata/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF50"/>
+  <dimension ref="A1:AF61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -4669,22 +4669,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>葛布一覽</t>
+          <t>樟蟲一覽</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>クズフ イチラン</t>
+          <t>ゲンジキムシ イチラン</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>鶴田清次, 佐々井半十郎撰 ; 中嶋仰山画 ; 鶴田清次校訂</t>
+          <t>信夫粲編選 ; 菅蒼圃図画</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4713,17 +4713,17 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>第7</t>
+          <t>第5</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b45ec8ae-8150-0e07-5a2c-534842461bdf.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/75fdfc46-592a-3735-8b60-0124d9336d6b.json</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>b45ec8ae-8150-0e07-5a2c-534842461bdf</t>
+          <t>75fdfc46-592a-3735-8b60-0124d9336d6b</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/b45ec8ae-8150-0e07-5a2c-534842461bdf</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/75fdfc46-592a-3735-8b60-0124d9336d6b</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/48a7ac5e4b66bd80f084292103bfe94e8a304f46.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d4650423dc021a555f9259142f68ca878542528a.jpg</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541452</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249041</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4771,7 +4771,7 @@
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b45ec8ae-8150-0e07-5a2c-534842461bdf/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/75fdfc46-592a-3735-8b60-0124d9336d6b/manifest</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
@@ -4785,22 +4785,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>草綿一覽</t>
+          <t>野蠺一覽</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>キワタ イチラン</t>
+          <t>ヤママユ イチラン</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>鶴田清次, 佐々井半十郎撰 ; 中嶋仰山画</t>
+          <t>信夫粲述 ; 菅蒼圃画</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4829,17 +4829,17 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>第9</t>
+          <t>第6</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca42ae46-852b-0252-00f5-21532b2f0284.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/758d0608-2902-6709-6a01-3f4cf8016f07.json</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>ca42ae46-852b-0252-00f5-21532b2f0284</t>
+          <t>758d0608-2902-6709-6a01-3f4cf8016f07</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/ca42ae46-852b-0252-00f5-21532b2f0284</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/758d0608-2902-6709-6a01-3f4cf8016f07</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f31f62c6e4b3bd21ba8a9858096a6dcb266b32e9.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a44be9e9f65dc9b92467da2db5650a4079a91748.jpg</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541451</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249042</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4887,7 +4887,7 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca42ae46-852b-0252-00f5-21532b2f0284/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/758d0608-2902-6709-6a01-3f4cf8016f07/manifest</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
@@ -4901,22 +4901,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>索麪一覽</t>
+          <t>葛布一覽</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ソウメン イチラン</t>
+          <t>クズフ イチラン</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>丹波修治著 ; 溝口月耕畫 ; 小森頼信増訂</t>
+          <t>鶴田清次, 佐々井半十郎撰 ; 中嶋仰山画 ; 鶴田清次校訂</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1876.3</t>
+          <t>1876.2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4945,17 +4945,17 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>第11</t>
+          <t>第7</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08719368-6196-1967-8516-881e2ad272ec.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b45ec8ae-8150-0e07-5a2c-534842461bdf.json</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>08719368-6196-1967-8516-881e2ad272ec</t>
+          <t>b45ec8ae-8150-0e07-5a2c-534842461bdf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/08719368-6196-1967-8516-881e2ad272ec</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/b45ec8ae-8150-0e07-5a2c-534842461bdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/75840e3939010d48da19c6c4c91984b4c2956eda.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/48a7ac5e4b66bd80f084292103bfe94e8a304f46.jpg</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541450</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541452</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5003,7 +5003,7 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08719368-6196-1967-8516-881e2ad272ec/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b45ec8ae-8150-0e07-5a2c-534842461bdf/manifest</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -5017,22 +5017,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>製茶一覽</t>
+          <t>苧麻一覽</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>セイチャ イチラン</t>
+          <t>チョマ イチラン</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>加藤景孝編述 ; 山高信離校訂 ; 中嶋仰山校圖</t>
+          <t>武田昌次述 ; 山﨑董洤画</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>第15</t>
+          <t>第8</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5542ed13-6e94-1b4d-18ba-95c0f2857725.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9bf2420e-4b29-4c1e-514c-05aaa9029149.json</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>5542ed13-6e94-1b4d-18ba-95c0f2857725</t>
+          <t>9bf2420e-4b29-4c1e-514c-05aaa9029149</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/5542ed13-6e94-1b4d-18ba-95c0f2857725</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/9bf2420e-4b29-4c1e-514c-05aaa9029149</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/52405ea3694503c60d975548082c8eea0ad56f0f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac8759f1091cca28b900075e337bd22218d4ce51.jpg</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541449</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249043</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5119,7 +5119,7 @@
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5542ed13-6e94-1b4d-18ba-95c0f2857725/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9bf2420e-4b29-4c1e-514c-05aaa9029149/manifest</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
@@ -5133,17 +5133,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>蠟一覽</t>
+          <t>草綿一覽</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ロウ イチラン</t>
+          <t>キワタ イチラン</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>武田昌次述 ; 山崎董洤畫</t>
+          <t>鶴田清次, 佐々井半十郎撰 ; 中嶋仰山画</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>第19</t>
+          <t>第9</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a6d65c34-6b80-5852-921e-3149b544869f.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ca42ae46-852b-0252-00f5-21532b2f0284.json</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>a6d65c34-6b80-5852-921e-3149b544869f</t>
+          <t>ca42ae46-852b-0252-00f5-21532b2f0284</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/a6d65c34-6b80-5852-921e-3149b544869f</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/ca42ae46-852b-0252-00f5-21532b2f0284</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6ebbfa67bd8e1b87a3f5e859b84c4a99b7d9d421.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f31f62c6e4b3bd21ba8a9858096a6dcb266b32e9.jpg</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541448</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541451</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5235,7 +5235,7 @@
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a6d65c34-6b80-5852-921e-3149b544869f/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ca42ae46-852b-0252-00f5-21532b2f0284/manifest</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
@@ -5249,22 +5249,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>白柹一覽</t>
+          <t>纎緯草木一覽</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ツルシガキ イチラン</t>
+          <t>イトスジ ソウモク イチラン</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>山本章夫撰 ; 溝口月耕画</t>
+          <t>武田昌次撰  ; 山﨑董洤画 ; 武田昌次増訂</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>第20</t>
+          <t>第10</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d5c063c3-946c-2c95-5d1c-dbe6acee9686.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/14d39f42-0bcb-41c8-a792-9707dfa39a66.json</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>d5c063c3-946c-2c95-5d1c-dbe6acee9686</t>
+          <t>14d39f42-0bcb-41c8-a792-9707dfa39a66</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/d5c063c3-946c-2c95-5d1c-dbe6acee9686</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/14d39f42-0bcb-41c8-a792-9707dfa39a66</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2b59b20d425cd675aab3e0fd32f10255bad32486.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6e79bb853eff25a88417e3702fbdb1af21fbcbd3.jpg</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541447</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249044</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5351,7 +5351,7 @@
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d5c063c3-946c-2c95-5d1c-dbe6acee9686/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/14d39f42-0bcb-41c8-a792-9707dfa39a66/manifest</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
@@ -5365,22 +5365,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>疊表一覽</t>
+          <t>索麪一覽</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>タタミオモテ イチラン</t>
+          <t>ソウメン イチラン</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>山本秀夫述 ; 溝口月耕画</t>
+          <t>丹波修治著 ; 溝口月耕畫 ; 小森頼信増訂</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>第21</t>
+          <t>第11</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/21b0217b-2823-20e2-571c-b8a8ee779068.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08719368-6196-1967-8516-881e2ad272ec.json</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>21b0217b-2823-20e2-571c-b8a8ee779068</t>
+          <t>08719368-6196-1967-8516-881e2ad272ec</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/21b0217b-2823-20e2-571c-b8a8ee779068</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/08719368-6196-1967-8516-881e2ad272ec</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f931e0324bdc008878ec620c81e615abea2e4d1.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/75840e3939010d48da19c6c4c91984b4c2956eda.jpg</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541446</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541450</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5467,7 +5467,7 @@
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/21b0217b-2823-20e2-571c-b8a8ee779068/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08719368-6196-1967-8516-881e2ad272ec/manifest</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
@@ -5481,22 +5481,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>香蕈一覽</t>
+          <t>葛粉一覽</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>シイタケ イチラン</t>
+          <t>クズコ イチラン</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>丹波修治述 ; 溝口月耕画 ; 横川政利増訂</t>
+          <t>丹波修治識 ; 中島仰山画</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>第22</t>
+          <t>第12</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6535085a-0367-411a-9559-17a5c2df1991.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7a7634d9-942f-9998-0314-4822947145b5.json</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>6535085a-0367-411a-9559-17a5c2df1991</t>
+          <t>7a7634d9-942f-9998-0314-4822947145b5</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/6535085a-0367-411a-9559-17a5c2df1991</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/7a7634d9-942f-9998-0314-4822947145b5</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4b78ca672d74c507d035bc3246c28d19c942218a.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18b71aafdcabb4670fff29d5410da2dbaa095cbd.jpg</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541445</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249045</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5583,7 +5583,7 @@
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6535085a-0367-411a-9559-17a5c2df1991/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7a7634d9-942f-9998-0314-4822947145b5/manifest</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
@@ -5597,22 +5597,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>蜂蜜一覽</t>
+          <t>藍一覽</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ハチミツ イチラン</t>
+          <t>アイ イチラン</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>丹波修治編撰 ; 溝口月耕圖画 ; 小林常賀校訂</t>
+          <t>安岡百樹録 ; 狩野良信図 ;  高鋭一校閲</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5641,17 +5641,17 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>第24</t>
+          <t>第13</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7e2f103e-2ba6-6697-73f1-5694feab9c99.json</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd</t>
+          <t>7e2f103e-2ba6-6697-73f1-5694feab9c99</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/7e2f103e-2ba6-6697-73f1-5694feab9c99</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ea3a295485d6ae75b0259ebfa371edb771e63db7.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2393fff3859722942b6536edeb091bb2ca36fe62.jpg</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541444</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249046</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5699,7 +5699,7 @@
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7e2f103e-2ba6-6697-73f1-5694feab9c99/manifest</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
@@ -5713,22 +5713,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>油一覽</t>
+          <t>青花紙一覽</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>アブラ イチラン</t>
+          <t>アオバナガミ イチラン</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>武田昌次述 ; 服部雪齋画</t>
+          <t>山本章夫撰 ; 溝口月耕画</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5757,17 +5757,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>第25</t>
+          <t>第14</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f1717738-9be8-8282-5c59-b3bc730353e9.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9fc88465-4759-2772-a560-3af2d2cb055d.json</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>f1717738-9be8-8282-5c59-b3bc730353e9</t>
+          <t>9fc88465-4759-2772-a560-3af2d2cb055d</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/f1717738-9be8-8282-5c59-b3bc730353e9</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/9fc88465-4759-2772-a560-3af2d2cb055d</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4703243389cfebc77eccba4836ac18a8dd4c0cad.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/391f11b6710d3f154ce4eb1d8b9524b85027cec5.jpg</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541443</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249047</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5815,7 +5815,7 @@
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f1717738-9be8-8282-5c59-b3bc730353e9/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9fc88465-4759-2772-a560-3af2d2cb055d/manifest</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
@@ -5829,17 +5829,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>臙脂一覽</t>
+          <t>製茶一覽</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>エンシ イチラン</t>
+          <t>セイチャ イチラン</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>武田昌次述 ; 服部雪齋, 山嵜董洤画</t>
+          <t>加藤景孝編述 ; 山高信離校訂 ; 中嶋仰山校圖</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5873,17 +5873,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>第26</t>
+          <t>第15</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b418fac-6c99-2474-9dd5-e9f19d684ed7.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5542ed13-6e94-1b4d-18ba-95c0f2857725.json</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2b418fac-6c99-2474-9dd5-e9f19d684ed7</t>
+          <t>5542ed13-6e94-1b4d-18ba-95c0f2857725</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/2b418fac-6c99-2474-9dd5-e9f19d684ed7</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/5542ed13-6e94-1b4d-18ba-95c0f2857725</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1a34bda1338c94c2ce2e4232ed844db7aa2ddbb.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/52405ea3694503c60d975548082c8eea0ad56f0f.jpg</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541442</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541449</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5931,7 +5931,7 @@
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b418fac-6c99-2474-9dd5-e9f19d684ed7/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5542ed13-6e94-1b4d-18ba-95c0f2857725/manifest</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
@@ -5945,27 +5945,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>澱粉一覽</t>
+          <t>烟草一覽</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>クズコ イチラン</t>
+          <t>タバコ イチラン</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>武田昌次誌 ; 服部雪齋画</t>
+          <t>南部陳編撰 ; 狩野良信図画</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2枚(上・下)</t>
+          <t>1枚</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>第27, 28</t>
+          <t>第16</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9660d869-1768-9427-721a-5f5aab869f52.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4692ecc3-67a9-1b21-72e2-27adf7493d5e.json</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>9660d869-1768-9427-721a-5f5aab869f52</t>
+          <t>4692ecc3-67a9-1b21-72e2-27adf7493d5e</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/9660d869-1768-9427-721a-5f5aab869f52</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/4692ecc3-67a9-1b21-72e2-27adf7493d5e</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/834ea8fd67b358d8f019d9d039424120db6b8497.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2be1f5b25e515f9a21c692266c4b7585f08092a4.jpg</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541441</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249048</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6047,7 +6047,7 @@
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9660d869-1768-9427-721a-5f5aab869f52/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4692ecc3-67a9-1b21-72e2-27adf7493d5e/manifest</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
@@ -6055,28 +6055,28 @@
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>褐腐一覽</t>
+          <t>漆一覽</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>コンニャク イチラン</t>
+          <t>ウルシ イチラン</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>榊原芳野原稿 ; 武田昌次抄録 ; 服部雪齋画圖</t>
+          <t>武田昌次撰 ; 山嵜董洤図 ; 武田昌次校訂</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6105,17 +6105,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>第29</t>
+          <t>第17</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/635d6e46-1d9b-5151-6945-f707a7677497.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6037e7e9-46ec-325d-749d-b70782af44ab.json</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>635d6e46-1d9b-5151-6945-f707a7677497</t>
+          <t>6037e7e9-46ec-325d-749d-b70782af44ab</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/635d6e46-1d9b-5151-6945-f707a7677497</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/6037e7e9-46ec-325d-749d-b70782af44ab</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4067498a108cd35c38537ead0034b587087f36b8.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/07cce1988ff6768ba5ebbed99ad6d9b95f438386.jpg</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541440</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249049</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6163,7 +6163,7 @@
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/635d6e46-1d9b-5151-6945-f707a7677497/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6037e7e9-46ec-325d-749d-b70782af44ab/manifest</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -6177,22 +6177,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>豆腐一覽</t>
+          <t>蒔繪一覽</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>トウフ イチラン</t>
+          <t>マキエ イチラン</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>榊原芳野原稿 ; 武田昌次抄録 ; 服部雪齋畫</t>
+          <t>加藤景孝識 ; 狩野良信画 ; 石田為武校正</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1876.2</t>
+          <t>1876.2|明治9年2月</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>第30</t>
+          <t>第18</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a985acb-2162-416b-6a3f-104093617254.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8423f773-73c7-7910-70ef-0c1a1b1f6184.json</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>1a985acb-2162-416b-6a3f-104093617254</t>
+          <t>8423f773-73c7-7910-70ef-0c1a1b1f6184</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/1a985acb-2162-416b-6a3f-104093617254</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/8423f773-73c7-7910-70ef-0c1a1b1f6184</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6add93cdc4004d6c197ad7df27716a3d102f64e5.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f78711a6095296d027ac86f8b814ed694febe81d.jpg</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541439</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249050</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -6279,7 +6279,7 @@
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a985acb-2162-416b-6a3f-104093617254/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8423f773-73c7-7910-70ef-0c1a1b1f6184/manifest</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
@@ -6290,6 +6290,1282 @@
         <v>1</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>蠟一覽</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ロウ イチラン</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>武田昌次述 ; 山崎董洤畫</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>第19</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a6d65c34-6b80-5852-921e-3149b544869f.json</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>a6d65c34-6b80-5852-921e-3149b544869f</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/a6d65c34-6b80-5852-921e-3149b544869f</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6ebbfa67bd8e1b87a3f5e859b84c4a99b7d9d421.jpg</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541448</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a6d65c34-6b80-5852-921e-3149b544869f/manifest</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>白柹一覽</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ツルシガキ イチラン</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>山本章夫撰 ; 溝口月耕画</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>第20</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d5c063c3-946c-2c95-5d1c-dbe6acee9686.json</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>d5c063c3-946c-2c95-5d1c-dbe6acee9686</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/d5c063c3-946c-2c95-5d1c-dbe6acee9686</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2b59b20d425cd675aab3e0fd32f10255bad32486.jpg</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541447</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d5c063c3-946c-2c95-5d1c-dbe6acee9686/manifest</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>疊表一覽</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>タタミオモテ イチラン</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>山本秀夫述 ; 溝口月耕画</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>第21</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/21b0217b-2823-20e2-571c-b8a8ee779068.json</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>21b0217b-2823-20e2-571c-b8a8ee779068</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/21b0217b-2823-20e2-571c-b8a8ee779068</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f931e0324bdc008878ec620c81e615abea2e4d1.jpg</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541446</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>0122</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/21b0217b-2823-20e2-571c-b8a8ee779068/manifest</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>香蕈一覽</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>シイタケ イチラン</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>丹波修治述 ; 溝口月耕画 ; 横川政利増訂</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>第22</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6535085a-0367-411a-9559-17a5c2df1991.json</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6535085a-0367-411a-9559-17a5c2df1991</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/6535085a-0367-411a-9559-17a5c2df1991</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4b78ca672d74c507d035bc3246c28d19c942218a.jpg</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541445</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>0123</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6535085a-0367-411a-9559-17a5c2df1991/manifest</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>製紙一覽</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>セイシ イチラン</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>山本秀夫遺稿 ; 山本正夫増補 ; 服部雪斎図画 ; 田中芳男校閲</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1876.2|明治9年2月</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>第23</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b4c3e30-0c8a-34ed-82a2-5cc259bc61ae.json</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>9b4c3e30-0c8a-34ed-82a2-5cc259bc61ae</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/9b4c3e30-0c8a-34ed-82a2-5cc259bc61ae</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f8df040f9fd7fd160512d3427d56cde173c3275c.jpg</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249051</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>0124</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b4c3e30-0c8a-34ed-82a2-5cc259bc61ae/manifest</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>蜂蜜一覽</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ハチミツ イチラン</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>丹波修治編撰 ; 溝口月耕圖画 ; 小林常賀校訂</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>第24</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd.json</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ea3a295485d6ae75b0259ebfa371edb771e63db7.jpg</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541444</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>0125</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e29c4137-1ff0-7009-0fc0-2f0cdbaa8dbd/manifest</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>油一覽</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>アブラ イチラン</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>武田昌次述 ; 服部雪齋画</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>第25</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f1717738-9be8-8282-5c59-b3bc730353e9.json</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>f1717738-9be8-8282-5c59-b3bc730353e9</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/f1717738-9be8-8282-5c59-b3bc730353e9</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4703243389cfebc77eccba4836ac18a8dd4c0cad.jpg</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541443</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>0126</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f1717738-9be8-8282-5c59-b3bc730353e9/manifest</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>臙脂一覽</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>エンシ イチラン</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>武田昌次述 ; 服部雪齋, 山嵜董洤画</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>第26</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b418fac-6c99-2474-9dd5-e9f19d684ed7.json</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2b418fac-6c99-2474-9dd5-e9f19d684ed7</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/2b418fac-6c99-2474-9dd5-e9f19d684ed7</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f1a34bda1338c94c2ce2e4232ed844db7aa2ddbb.jpg</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541442</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b418fac-6c99-2474-9dd5-e9f19d684ed7/manifest</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>澱粉一覽</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>クズコ イチラン</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>武田昌次誌 ; 服部雪齋画</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2枚(上・下)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>第27, 28</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9660d869-1768-9427-721a-5f5aab869f52.json</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>9660d869-1768-9427-721a-5f5aab869f52</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/9660d869-1768-9427-721a-5f5aab869f52</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/834ea8fd67b358d8f019d9d039424120db6b8497.jpg</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541441</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9660d869-1768-9427-721a-5f5aab869f52/manifest</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>褐腐一覽</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>コンニャク イチラン</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>榊原芳野原稿 ; 武田昌次抄録 ; 服部雪齋画圖</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>第29</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/635d6e46-1d9b-5151-6945-f707a7677497.json</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>635d6e46-1d9b-5151-6945-f707a7677497</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/635d6e46-1d9b-5151-6945-f707a7677497</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4067498a108cd35c38537ead0034b587087f36b8.jpg</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541440</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>0129</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/635d6e46-1d9b-5151-6945-f707a7677497/manifest</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>豆腐一覽</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>トウフ イチラン</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>榊原芳野原稿 ; 武田昌次抄録 ; 服部雪齋畫</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1876.2</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1枚</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Farm Museum Collection</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>教草</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>第30</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a985acb-2162-416b-6a3f-104093617254.json</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1a985acb-2162-416b-6a3f-104093617254</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agrifarm/document/1a985acb-2162-416b-6a3f-104093617254</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6add93cdc4004d6c197ad7df27716a3d102f64e5.jpg</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541439</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>農場博物館コレクション</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a985acb-2162-416b-6a3f-104093617254/manifest</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
